--- a/output/full_scan/batch_seq1_2026-09-23.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-23.xlsx
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>242.366036936671</v>
+        <v>242.3660369366709</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>26.3</v>
